--- a/data/sinalizacao_placas.xlsx
+++ b/data/sinalizacao_placas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsulidario\Documents\VISUAL_SISTEMA\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486781EC-13E6-4E1C-A7B3-BDA32C860FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E361EB9C-CE2F-4ECD-ACE5-A340F58DBA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5386C7C1-27BE-46BD-BF1F-FD198ABF7DCE}"/>
   </bookViews>
@@ -2325,7 +2325,7 @@
       <c r="AH8" s="16"/>
       <c r="AI8" s="16"/>
     </row>
-    <row r="9" spans="1:35" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>43</v>
       </c>
@@ -2396,7 +2396,7 @@
       <c r="AH9" s="16"/>
       <c r="AI9" s="16"/>
     </row>
-    <row r="10" spans="1:35" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>43</v>
       </c>
@@ -2467,7 +2467,7 @@
       <c r="AH10" s="16"/>
       <c r="AI10" s="16"/>
     </row>
-    <row r="11" spans="1:35" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>48</v>
       </c>
@@ -2538,7 +2538,7 @@
       <c r="AH11" s="16"/>
       <c r="AI11" s="16"/>
     </row>
-    <row r="12" spans="1:35" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>51</v>
       </c>
@@ -2609,7 +2609,7 @@
       <c r="AH12" s="16"/>
       <c r="AI12" s="16"/>
     </row>
-    <row r="13" spans="1:35" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>53</v>
       </c>
@@ -4169,7 +4169,7 @@
       <c r="AH34" s="3"/>
       <c r="AI34" s="3"/>
     </row>
-    <row r="35" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:35" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>107</v>
       </c>
@@ -4182,13 +4182,13 @@
       <c r="D35" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="9">
         <v>224.3</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="9" t="s">
         <v>105</v>
       </c>
       <c r="H35" s="13" t="s">
@@ -4218,7 +4218,7 @@
       <c r="P35" s="17">
         <v>2</v>
       </c>
-      <c r="Q35" s="21" t="s">
+      <c r="Q35" s="13" t="s">
         <v>109</v>
       </c>
       <c r="R35" s="16"/>

--- a/data/sinalizacao_placas.xlsx
+++ b/data/sinalizacao_placas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsulidario\Documents\VISUAL_SISTEMA\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E361EB9C-CE2F-4ECD-ACE5-A340F58DBA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1DD9BE-707E-47F0-95FC-055E85805BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5386C7C1-27BE-46BD-BF1F-FD198ABF7DCE}"/>
   </bookViews>
@@ -2856,8 +2856,8 @@
       <c r="K16" s="13">
         <v>1</v>
       </c>
-      <c r="L16" s="13">
-        <v>1</v>
+      <c r="L16" s="14">
+        <v>0</v>
       </c>
       <c r="M16" s="10">
         <v>1</v>
@@ -8460,8 +8460,8 @@
       <c r="K96" s="23">
         <v>1</v>
       </c>
-      <c r="L96" s="23">
-        <v>1</v>
+      <c r="L96" s="14">
+        <v>0</v>
       </c>
       <c r="M96" s="23">
         <v>1</v>
